--- a/stockwebscrapper/stock_prices.xlsx
+++ b/stockwebscrapper/stock_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$3.01</t>
+          <t>$20.22</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$30.85</t>
+          <t>$36.37</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$47.50</t>
+          <t>$54.91</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$12.16</t>
+          <t>$11.75</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$5.51</t>
+          <t>$5.31</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VRN:TSE</t>
+          <t>WCP:TSE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$7.17</t>
+          <t>$10.44</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$1.96</t>
+          <t>$1.90</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$13.67</t>
+          <t>$17.29</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$22.25</t>
+          <t>$19.61</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$50.71</t>
+          <t>$56.56</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>$20.11</t>
+          <t>$25.64</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>$6.03</t>
+          <t>$7.38</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>$2.27</t>
+          <t>$2.31</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$31.22</t>
+          <t>$20.36</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$1.25</t>
+          <t>$6.06</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$34.47</t>
+          <t>$38.20</t>
         </is>
       </c>
     </row>
@@ -686,12 +686,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMAT:NASDAQ</t>
+          <t>VCNX:OTCMKTS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$163.64</t>
+          <t>$0.45</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OGI:TSE</t>
+          <t>AMAT:NASDAQ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$2.27</t>
+          <t>$164.39</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>POU:TSE</t>
+          <t>OGI:TSE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$31.22</t>
+          <t>$2.31</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,117 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>POU:TSE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>$20.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>QQC:TSE</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>$36.15</t>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>$38.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>XUS:TSE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>$55.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>XIC:TSE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>$45.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>XMC:TSE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>$34.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>XHU:TSE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>$34.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>XDIV:TSE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>$33.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>XEQT:TSE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>$37.43</t>
         </is>
       </c>
     </row>

--- a/stockwebscrapper/stock_prices.xlsx
+++ b/stockwebscrapper/stock_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$20.22</t>
+          <t>$23.04</t>
         </is>
       </c>
     </row>
@@ -461,12 +461,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HUT:TSE</t>
+          <t>GWO:TSE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$36.37</t>
+          <t>$62.04</t>
         </is>
       </c>
     </row>
@@ -476,12 +476,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GWO:TSE</t>
+          <t>CGX:TSE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$54.91</t>
+          <t>$10.50</t>
         </is>
       </c>
     </row>
@@ -491,12 +491,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CGX:TSE</t>
+          <t>BB:TSE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$11.75</t>
+          <t>$4.67</t>
         </is>
       </c>
     </row>
@@ -506,12 +506,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BB:TSE</t>
+          <t>WCP:TSE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$5.31</t>
+          <t>$13.87</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WCP:TSE</t>
+          <t>TLRY:TSE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$10.44</t>
+          <t>$9.83</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TLRY:TSE</t>
+          <t>PXT:TSE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$1.90</t>
+          <t>$23.15</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PXT:TSE</t>
+          <t>AC:TSE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$17.29</t>
+          <t>$17.67</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AC:TSE</t>
+          <t>XMA:TSE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$19.61</t>
+          <t>$48.86</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SU:TSE</t>
+          <t>BEN:NYSE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$56.56</t>
+          <t>$26.24</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BEN:NYSE</t>
+          <t>ACB:TSE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>$25.64</t>
+          <t>$4.78</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ACB:TSE</t>
+          <t>OGI:TSE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>$7.38</t>
+          <t>$2.01</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OGI:TSE</t>
+          <t>POU:TSE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>$2.31</t>
+          <t>$29.34</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>POU:TSE</t>
+          <t>ASM:TSE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$20.36</t>
+          <t>$10.59</t>
         </is>
       </c>
     </row>
@@ -656,12 +656,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ASM:TSE</t>
+          <t>QCLN:NASDAQ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$6.06</t>
+          <t>$45.02</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>QCLN:NASDAQ</t>
+          <t>VCNX:OTCMKTS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$38.20</t>
+          <t>$0.80</t>
         </is>
       </c>
     </row>
@@ -686,12 +686,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VCNX:OTCMKTS</t>
+          <t>AMAT:NASDAQ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$0.45</t>
+          <t>$324.74</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMAT:NASDAQ</t>
+          <t>OGI:TSE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$164.39</t>
+          <t>$2.01</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OGI:TSE</t>
+          <t>POU:TSE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$2.31</t>
+          <t>$29.34</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>POU:TSE</t>
+          <t>QQC:TSE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$20.36</t>
+          <t>$39.84</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>QQC:TSE</t>
+          <t>XUS:TSE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$38.64</t>
+          <t>$56.61</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XUS:TSE</t>
+          <t>XIC:TSE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$55.43</t>
+          <t>$52.93</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>XIC:TSE</t>
+          <t>XMC:TSE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>$45.47</t>
+          <t>$35.51</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>XMC:TSE</t>
+          <t>XHU:TSE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$34.61</t>
+          <t>$37.42</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>XHU:TSE</t>
+          <t>XDIV:TSE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$34.36</t>
+          <t>$38.23</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>XDIV:TSE</t>
+          <t>XEQT:TSE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$33.26</t>
+          <t>$40.24</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>XEQT:TSE</t>
+          <t>VDY:TSE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$37.43</t>
+          <t>$65.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TGRO:TSE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>$26.64</t>
         </is>
       </c>
     </row>

--- a/stockwebscrapper/stock_prices.xlsx
+++ b/stockwebscrapper/stock_prices.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,438 +413,438 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CHR:TSE</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CHR:TSE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>$23.04</t>
+          <t>$28.32</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GWO:TSE</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GWO:TSE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>$62.04</t>
+          <t>$93.52</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CGX:TSE</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CGX:TSE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>$10.50</t>
+          <t>$12.39</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BB:TSE</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BB:TSE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>$4.67</t>
+          <t>$11.16</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WCP:TSE</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WCP:TSE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>$13.87</t>
+          <t>$18.86</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TLRY:TSE</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TLRY:TSE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>$9.83</t>
+          <t>$5.59</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PXT:TSE</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PXT:TSE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>$23.15</t>
+          <t>$28.36</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AC:TSE</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AC:TSE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>$17.67</t>
+          <t>$28.26</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>XMA:TSE</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XMA:TSE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>$48.86</t>
+          <t>$48.67</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BEN:NYSE</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BEN:NYSE</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>$26.24</t>
+          <t>$33.01</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ACB:TSE</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ACB:TSE</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>$4.78</t>
+          <t>$5.40</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OGI:TSE</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>$1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>POU:TSE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>$32.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ASM:TSE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>$8.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QCLN:NASDAQ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>$47.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>VCNX:OTCMKTS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>$1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AMAT:NASDAQ</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>$444.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>OGI:TSE</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>$2.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>$1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>POU:TSE</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>$29.34</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ASM:TSE</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>$10.59</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>QCLN:NASDAQ</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>$45.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>VCNX:OTCMKTS</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>$0.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>AMAT:NASDAQ</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>$324.74</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>OGI:TSE</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>$2.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>POU:TSE</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>$29.34</t>
+          <t>$32.21</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QQC:TSE</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>QQC:TSE</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>$39.84</t>
+          <t>$49.31</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>XUS:TSE</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>XUS:TSE</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>$56.61</t>
+          <t>$66.17</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>XIC:TSE</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XIC:TSE</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>$52.93</t>
+          <t>$57.33</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>XMC:TSE</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>XMC:TSE</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>$35.51</t>
+          <t>$39.24</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>XHU:TSE</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>XHU:TSE</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>$37.42</t>
+          <t>$41.04</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>XDIV:TSE</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>XDIV:TSE</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>$38.23</t>
+          <t>$46.31</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>XEQT:TSE</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>XEQT:TSE</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>$40.24</t>
+          <t>$45.41</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>VDY:TSE</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VDY:TSE</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>$65.94</t>
+          <t>$77.17</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TGRO:TSE</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TGRO:TSE</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>$26.64</t>
+          <t>$29.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>XEI:TSE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>$39.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IONQ:NYSE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>$39.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AKT:TSE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>$3.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HURA:TSE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>$47.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ZEQT:TSE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>$23.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CHPS:TSE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>$84.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TEC:TSE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>$62.46</t>
         </is>
       </c>
     </row>

--- a/stockwebscrapper/stock_prices.xlsx
+++ b/stockwebscrapper/stock_prices.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +431,11 @@
           <t>price</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>captured_at</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -436,8 +445,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$28.32</t>
-        </is>
+          <t>$30.50</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="3">
@@ -448,8 +460,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$93.52</t>
-        </is>
+          <t>$92.88</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="4">
@@ -460,8 +475,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$12.39</t>
-        </is>
+          <t>$13.08</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="5">
@@ -472,8 +490,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$11.16</t>
-        </is>
+          <t>$11.49</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="6">
@@ -484,8 +505,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$18.86</t>
-        </is>
+          <t>$18.31</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="7">
@@ -496,8 +520,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$5.59</t>
-        </is>
+          <t>$5.71</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="8">
@@ -508,8 +535,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$28.36</t>
-        </is>
+          <t>$27.23</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="9">
@@ -520,8 +550,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$28.26</t>
-        </is>
+          <t>$26.19</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="10">
@@ -532,8 +565,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$48.67</t>
-        </is>
+          <t>$46.41</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="11">
@@ -544,8 +580,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$33.01</t>
-        </is>
+          <t>$32.40</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="12">
@@ -556,8 +595,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$5.40</t>
-        </is>
+          <t>$5.71</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="13">
@@ -568,8 +610,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>$1.44</t>
-        </is>
+          <t>$1.55</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="14">
@@ -580,8 +625,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$32.21</t>
-        </is>
+          <t>$29.88</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="15">
@@ -592,8 +640,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$8.94</t>
-        </is>
+          <t>$7.99</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="16">
@@ -604,8 +655,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>$47.82</t>
-        </is>
+          <t>$47.70</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="17">
@@ -616,8 +670,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>$1.00</t>
-        </is>
+          <t>$0.97</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="18">
@@ -628,8 +685,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>$444.57</t>
-        </is>
+          <t>$474.01</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="19">
@@ -640,8 +700,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>$1.44</t>
-        </is>
+          <t>$1.55</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="20">
@@ -652,8 +715,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$32.21</t>
-        </is>
+          <t>$29.88</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="21">
@@ -664,8 +730,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$49.31</t>
-        </is>
+          <t>$50.71</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="22">
@@ -676,8 +745,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>$66.17</t>
-        </is>
+          <t>$67.22</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="23">
@@ -688,8 +760,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>$57.33</t>
-        </is>
+          <t>$56.49</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="24">
@@ -700,8 +775,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>$39.24</t>
-        </is>
+          <t>$39.40</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="25">
@@ -712,8 +790,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>$41.04</t>
-        </is>
+          <t>$40.64</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="26">
@@ -724,8 +805,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>$46.31</t>
-        </is>
+          <t>$45.69</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="27">
@@ -736,8 +820,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>$45.41</t>
-        </is>
+          <t>$45.59</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="28">
@@ -748,8 +835,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>$77.17</t>
-        </is>
+          <t>$76.28</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="29">
@@ -760,8 +850,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>$29.43</t>
-        </is>
+          <t>$29.69</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="30">
@@ -772,8 +865,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>$39.75</t>
-        </is>
+          <t>$39.02</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="31">
@@ -784,8 +880,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>$39.13</t>
-        </is>
+          <t>$45.95</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="32">
@@ -796,8 +895,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>$3.81</t>
-        </is>
+          <t>$3.71</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="33">
@@ -808,8 +910,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>$47.50</t>
-        </is>
+          <t>$46.50</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="34">
@@ -820,8 +925,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>$23.39</t>
-        </is>
+          <t>$23.54</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="35">
@@ -832,8 +940,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>$84.14</t>
-        </is>
+          <t>$87.97</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
     <row r="36">
@@ -844,8 +955,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>$62.46</t>
-        </is>
+          <t>$63.95</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46293.62980238415</v>
       </c>
     </row>
   </sheetData>
